--- a/public/samples/sheets/sales-performance-2026.xlsx
+++ b/public/samples/sheets/sales-performance-2026.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20000" windowHeight="12000" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Dashboard" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Orders" state="visible" r:id="rId5"/>
@@ -11,6 +14,28 @@
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2155,11 +2180,11 @@
         <f>SUMIFS(Orders!$I:$I,Orders!$G:$G,G9)</f>
         <v>245539</v>
       </c>
-      <c r="J9" t="str">
+      <c r="J9" cm="1" t="str">
         <f t="array" ref="J9:J14">_xlfn.SORTBY(Reps!A2:A7,Reps!D2:D7,-1)</f>
         <v>Asha Rao</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" cm="1" s="9">
         <f t="array" ref="K9:K14">_xlfn.SORTBY(Reps!D2:D7,Reps!D2:D7,-1)</f>
         <v>93973</v>
       </c>
@@ -2415,7 +2440,7 @@
         <f>SUMIFS(Orders!$I:$I,Orders!$C:$C,E$8,Orders!$B:$B,"&gt;="&amp;$A18,Orders!$B:$B,"&lt;"&amp;EDATE($A18,1))</f>
         <v>19347</v>
       </c>
-      <c r="J18" t="str">
+      <c r="J18" cm="1" t="str">
         <f t="array" ref="J18:J30">_xlfn._xlws.FILTER(Orders!A2:A241,(Orders!L2:L241="Open")*(Orders!I2:I241&gt;3000),"None")</f>
         <v>SO-10089</v>
       </c>
@@ -12929,7 +12954,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DA61B58E-4CFB-4CFB-ACF9-31F37B3C81FC}</x14:id>
+          <x14:id>{893AFB3D-34B8-40DA-98AB-4D5240CAC014}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12960,7 +12985,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DA61B58E-4CFB-4CFB-ACF9-31F37B3C81FC}">
+          <x14:cfRule type="dataBar" id="{893AFB3D-34B8-40DA-98AB-4D5240CAC014}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -13473,7 +13498,7 @@
       <drawing r:id="rIdDrawing1"/>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9C49B82E-AD77-4999-9DAB-E82CB597C87C}</x14:id>
+          <x14:id>{79893254-C896-4070-8C58-304D17CA6AD7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13484,7 +13509,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9C49B82E-AD77-4999-9DAB-E82CB597C87C}">
+          <x14:cfRule type="dataBar" id="{79893254-C896-4070-8C58-304D17CA6AD7}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
